--- a/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
+++ b/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
@@ -5,18 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\DeSales\SWE\Documents\Andrew Presta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\DeSales\SWE\Documents\AndrewPrestaWeeklyLogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8637A16-831F-4052-899C-4DD62B149EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B5DE3F-454D-4157-ABE2-B125D69AE99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="14" r:id="rId1"/>
     <sheet name="Jan 22-28" sheetId="1" r:id="rId2"/>
     <sheet name="Jan 29-Feb 4" sheetId="2" r:id="rId3"/>
     <sheet name="Feb 4-Feb 8" sheetId="17" r:id="rId4"/>
+    <sheet name="Feb 8-Feb 15" sheetId="19" r:id="rId5"/>
+    <sheet name="Feb 15 -Feb 22" sheetId="20" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
   <si>
     <t>Date on which you worked on the project.</t>
   </si>
@@ -96,6 +98,31 @@
     <t>1. Developed 3 functional requirements based on user stories.
 2. Outlined functional requirements to fit the project with a description, response sequence, and dependencies.
 3. Began formulating ideas on conversion to use cases from the functional requirements.</t>
+  </si>
+  <si>
+    <t>2/9/26, 2/11/26, 2/13/26</t>
+  </si>
+  <si>
+    <t>1, 1, 1</t>
+  </si>
+  <si>
+    <t>3.3.1, 3.3.7, 3.3.8, 3.4.5, 3.4.6, 4.1.1, 4.1.7, 4.1.8</t>
+  </si>
+  <si>
+    <t>1. Developed use cases for viewing test questions, selecting answers, and submitting a test.
+2. Made non-functional requirements for maintainability and portability.
+3. Started diagrams for use case 1, 7, and 8.</t>
+  </si>
+  <si>
+    <t>3.3.1, 3.3.7, 3.3.8, 4.1.1, 4.1.7, 4.1.8</t>
+  </si>
+  <si>
+    <t>1. Slightly improved use cases for viewing test questions, selecting answers, and submitting a test.
+2. Improved SRS document as a whole to adjust wording issues and font choices.
+3. Finished diagrams for use case 1, 7, and 8.</t>
+  </si>
+  <si>
+    <t>2/16/26, 2/18/26, 2/20/26</t>
   </si>
 </sst>
 </file>
@@ -189,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -262,9 +289,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1202,7 +1226,7 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="16"/>
-      <c r="N5" s="26" t="s">
+      <c r="N5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="O5" s="22"/>
@@ -1266,6 +1290,494 @@
       <c r="M7" s="4"/>
       <c r="N7" s="8">
         <v>2</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="19"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="25"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="23"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="13"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="8">
+        <v>3</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="19"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="25"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="23"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="13"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="8">
+        <v>3</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>

--- a/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
+++ b/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\DeSales\SWE\Documents\AndrewPrestaWeeklyLogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D436F4-262E-476F-AA6B-16C9C014726A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43852EA2-4AE9-4CCF-BFF4-547316771E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="14" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Feb 8-Feb 15" sheetId="19" r:id="rId5"/>
     <sheet name="Feb 15 -Feb 22" sheetId="20" r:id="rId6"/>
     <sheet name="Feb 22-Mar 1" sheetId="21" r:id="rId7"/>
+    <sheet name="Mar 1 - Mar 8" sheetId="22" r:id="rId8"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="32">
   <si>
     <t>Date on which you worked on the project.</t>
   </si>
@@ -132,6 +133,17 @@
     <t>1. Began working on the domain model for use case 1.
 2. Created class objects for all parts of the system for use case 1 including TestController, Test, Lesson, Selection, etc.
 3. Connected the components in an attempt to avoid coupling and provide a logical separation of concerns.</t>
+  </si>
+  <si>
+    <t>3/2/2026, 3/4/2026, 3/6/2026</t>
+  </si>
+  <si>
+    <t>2.1, 2.2.3, 3.5, 3.6</t>
+  </si>
+  <si>
+    <t>1. Finished the domain model for use case 1.
+2. Added concept attributes for Question, AnswerChoice, TestController, Lesson, and QuestionStorage.
+3. Added Selection component and TestController component.</t>
   </si>
 </sst>
 </file>
@@ -228,16 +240,16 @@
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -246,17 +258,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -276,14 +291,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -292,12 +310,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -607,53 +619,53 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" s="1" customFormat="1" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="2" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="4"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="5">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22">
         <v>46043</v>
       </c>
       <c r="O2" s="6"/>
@@ -669,22 +681,22 @@
       <c r="Y2" s="7"/>
     </row>
     <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="8">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5">
         <v>1</v>
       </c>
       <c r="O3" s="6"/>
@@ -700,22 +712,22 @@
       <c r="Y3" s="7"/>
     </row>
     <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="8" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="O4" s="6"/>
@@ -731,22 +743,22 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="8" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="O5" s="6"/>
@@ -762,53 +774,53 @@
       <c r="Y5" s="7"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="8">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
         <v>1</v>
       </c>
       <c r="O7" s="6"/>
@@ -826,6 +838,12 @@
     <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A7:M7"/>
@@ -834,12 +852,6 @@
     <mergeCell ref="N6:Y6"/>
     <mergeCell ref="N5:Y5"/>
     <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="N3:Y3"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -852,84 +864,84 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="2" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="4"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="5">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22">
         <v>46055</v>
       </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="22"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="8">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5">
         <v>1</v>
       </c>
       <c r="O3" s="6"/>
@@ -945,22 +957,22 @@
       <c r="Y3" s="7"/>
     </row>
     <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="8" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="O4" s="6"/>
@@ -976,85 +988,329 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="23" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="25"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="8">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
         <v>1</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>2</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1090,91 +1346,91 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="2" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="4"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="22"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="8" t="s">
-        <v>18</v>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1189,22 +1445,22 @@
       <c r="Y3" s="7"/>
     </row>
     <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="8" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="O4" s="6"/>
@@ -1220,85 +1476,85 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="25"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="17"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="8">
-        <v>2</v>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1334,90 +1590,90 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="2" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="4"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="22"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="8" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="O3" s="6"/>
@@ -1433,22 +1689,22 @@
       <c r="Y3" s="7"/>
     </row>
     <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="8" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="O4" s="6"/>
@@ -1464,84 +1720,84 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="25"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="17"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="8">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
         <v>3</v>
       </c>
       <c r="O7" s="6"/>
@@ -1578,91 +1834,91 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="2" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="4"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="22"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22">
+        <v>46082</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="8" t="s">
-        <v>21</v>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5">
+        <v>1</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1677,23 +1933,23 @@
       <c r="Y3" s="7"/>
     </row>
     <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="8" t="s">
-        <v>13</v>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -1708,85 +1964,85 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="25"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="17"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="8">
-        <v>3</v>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>1</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1822,91 +2078,91 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="2" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="4"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="5">
-        <v>46082</v>
-      </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="22"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="8">
-        <v>1</v>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1921,22 +2177,22 @@
       <c r="Y3" s="7"/>
     </row>
     <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="8" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
         <v>27</v>
       </c>
       <c r="O4" s="6"/>
@@ -1952,85 +2208,85 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="8">
-        <v>2.1</v>
-      </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="25"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="17"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="8">
-        <v>1</v>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>

--- a/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
+++ b/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\DeSales\SWE\Documents\AndrewPrestaWeeklyLogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43852EA2-4AE9-4CCF-BFF4-547316771E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E8D1BB-B912-48E0-B985-64FD45FBF68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="14" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Feb 15 -Feb 22" sheetId="20" r:id="rId6"/>
     <sheet name="Feb 22-Mar 1" sheetId="21" r:id="rId7"/>
     <sheet name="Mar 1 - Mar 8" sheetId="22" r:id="rId8"/>
+    <sheet name="Mar 15 - Mar 22" sheetId="24" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="37">
   <si>
     <t>Date on which you worked on the project.</t>
   </si>
@@ -144,6 +145,23 @@
     <t>1. Finished the domain model for use case 1.
 2. Added concept attributes for Question, AnswerChoice, TestController, Lesson, and QuestionStorage.
 3. Added Selection component and TestController component.</t>
+  </si>
+  <si>
+    <t>Sprint Planning</t>
+  </si>
+  <si>
+    <t>3/16/2026, 3/18/2026, 3/20/2026</t>
+  </si>
+  <si>
+    <t>2.1, 2.2, 2.3</t>
+  </si>
+  <si>
+    <t>1, 2, 2</t>
+  </si>
+  <si>
+    <t>1. Filled out use case #4 tasks and acceptance criteria.
+2. Assigned a task for use case #2 and #6.
+3. Started implementing the previous IDE and terminal in a clean and structured way.</t>
   </si>
 </sst>
 </file>
@@ -838,12 +856,6 @@
     <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="N3:Y3"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A7:M7"/>
@@ -852,6 +864,12 @@
     <mergeCell ref="N6:Y6"/>
     <mergeCell ref="N5:Y5"/>
     <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1067,6 +1085,250 @@
       <c r="M7" s="4"/>
       <c r="N7" s="5">
         <v>1</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>2</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1102,8 +1364,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1155,7 +1417,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1186,7 +1448,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1248,7 +1510,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1279,7 +1541,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1310,7 +1572,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1346,8 +1608,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1399,7 +1661,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1492,7 +1754,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1523,7 +1785,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1590,8 +1852,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1642,8 +1904,8 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22" t="s">
-        <v>26</v>
+      <c r="N2" s="22">
+        <v>46082</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1673,8 +1935,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5" t="s">
-        <v>21</v>
+      <c r="N3" s="5">
+        <v>1</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1705,7 +1967,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -1735,8 +1997,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>24</v>
+      <c r="N5" s="5">
+        <v>2.1</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1767,7 +2029,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1798,7 +2060,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1834,8 +2096,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1886,8 +2148,8 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22">
-        <v>46082</v>
+      <c r="N2" s="22" t="s">
+        <v>29</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1917,8 +2179,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5">
-        <v>1</v>
+      <c r="N3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1979,8 +2241,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5">
-        <v>2.1</v>
+      <c r="N5" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2011,7 +2273,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2042,7 +2304,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -2078,8 +2340,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA70D48-0F63-40A7-A614-2A774FBC305E}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2131,7 +2393,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -2162,7 +2424,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -2193,7 +2455,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -2224,7 +2486,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2255,7 +2517,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2286,7 +2548,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>

--- a/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
+++ b/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\DeSales\SWE\Documents\AndrewPrestaWeeklyLogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43852EA2-4AE9-4CCF-BFF4-547316771E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58657684-F074-4737-9654-1CF329F05F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="14" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="Feb 15 -Feb 22" sheetId="20" r:id="rId6"/>
     <sheet name="Feb 22-Mar 1" sheetId="21" r:id="rId7"/>
     <sheet name="Mar 1 - Mar 8" sheetId="22" r:id="rId8"/>
+    <sheet name="Mar 15 - Mar 22" sheetId="24" r:id="rId9"/>
+    <sheet name="Mar 22 - Mar 29" sheetId="25" r:id="rId10"/>
+    <sheet name="Mar 29 - Apr 12" sheetId="26" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="45">
   <si>
     <t>Date on which you worked on the project.</t>
   </si>
@@ -144,6 +147,50 @@
     <t>1. Finished the domain model for use case 1.
 2. Added concept attributes for Question, AnswerChoice, TestController, Lesson, and QuestionStorage.
 3. Added Selection component and TestController component.</t>
+  </si>
+  <si>
+    <t>Sprint Planning</t>
+  </si>
+  <si>
+    <t>3/16/2026, 3/18/2026, 3/20/2026</t>
+  </si>
+  <si>
+    <t>2.1, 2.2, 2.3</t>
+  </si>
+  <si>
+    <t>1, 2, 2</t>
+  </si>
+  <si>
+    <t>1. Filled out use case #4 tasks and acceptance criteria.
+2. Assigned a task for use case #2 and #6.
+3. Started implementing the previous IDE and terminal in a clean and structured way.</t>
+  </si>
+  <si>
+    <t>3/23/2026, 3/25/2026, 3/27/2026</t>
+  </si>
+  <si>
+    <t>1. Continued implementing the previous IDE and terminal in a clean and structured way.
+2. Created classes for registering and getting a single socket, and registering input and output.
+3. Created classes for ProcessManager and TerminalManager for handling streaming and writing to terminal respectively.
+4. Created more separation handlers and a test class to run the code.</t>
+  </si>
+  <si>
+    <t>3/30/2026, 4/1/2026, 4/3/2026</t>
+  </si>
+  <si>
+    <t>1, 4, 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, </t>
+  </si>
+  <si>
+    <t>Use Case #4: Using IDE</t>
+  </si>
+  <si>
+    <t>1. Met with the team to pick tasks and develop the Spring Planning document</t>
+  </si>
+  <si>
+    <t>Sprint Planning, Use Case #4: Using IDE</t>
   </si>
 </sst>
 </file>
@@ -613,6 +660,494 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD054709-500D-4F76-8B36-C67C0620C98A}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>8</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD70740-6FBF-43AF-83B0-7173CE1966F2}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>6</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y8"/>
@@ -2320,4 +2855,248 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA70D48-0F63-40A7-A614-2A774FBC305E}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>5</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
+++ b/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\DeSales\SWE\Documents\AndrewPrestaWeeklyLogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E8D1BB-B912-48E0-B985-64FD45FBF68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58657684-F074-4737-9654-1CF329F05F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="14" r:id="rId1"/>
@@ -22,6 +22,8 @@
     <sheet name="Feb 22-Mar 1" sheetId="21" r:id="rId7"/>
     <sheet name="Mar 1 - Mar 8" sheetId="22" r:id="rId8"/>
     <sheet name="Mar 15 - Mar 22" sheetId="24" r:id="rId9"/>
+    <sheet name="Mar 22 - Mar 29" sheetId="25" r:id="rId10"/>
+    <sheet name="Mar 29 - Apr 12" sheetId="26" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="45">
   <si>
     <t>Date on which you worked on the project.</t>
   </si>
@@ -162,6 +164,33 @@
     <t>1. Filled out use case #4 tasks and acceptance criteria.
 2. Assigned a task for use case #2 and #6.
 3. Started implementing the previous IDE and terminal in a clean and structured way.</t>
+  </si>
+  <si>
+    <t>3/23/2026, 3/25/2026, 3/27/2026</t>
+  </si>
+  <si>
+    <t>1. Continued implementing the previous IDE and terminal in a clean and structured way.
+2. Created classes for registering and getting a single socket, and registering input and output.
+3. Created classes for ProcessManager and TerminalManager for handling streaming and writing to terminal respectively.
+4. Created more separation handlers and a test class to run the code.</t>
+  </si>
+  <si>
+    <t>3/30/2026, 4/1/2026, 4/3/2026</t>
+  </si>
+  <si>
+    <t>1, 4, 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, </t>
+  </si>
+  <si>
+    <t>Use Case #4: Using IDE</t>
+  </si>
+  <si>
+    <t>1. Met with the team to pick tasks and develop the Spring Planning document</t>
+  </si>
+  <si>
+    <t>Sprint Planning, Use Case #4: Using IDE</t>
   </si>
 </sst>
 </file>
@@ -631,12 +660,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD054709-500D-4F76-8B36-C67C0620C98A}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
@@ -683,20 +712,20 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22">
-        <v>46043</v>
-      </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="7"/>
+      <c r="N2" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -714,8 +743,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5">
-        <v>1</v>
+      <c r="N3" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -746,7 +775,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -776,20 +805,20 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="7"/>
+      <c r="N5" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
@@ -808,7 +837,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -839,252 +868,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>1</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="N7:Y7"/>
-    <mergeCell ref="N6:Y6"/>
-    <mergeCell ref="N5:Y5"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="N3:Y3"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
-    </row>
-    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="22">
-        <v>46055</v>
-      </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="24"/>
-    </row>
-    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5">
-        <v>1</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="12"/>
-    </row>
-    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="18"/>
-    </row>
-    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1120,8 +904,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD70740-6FBF-43AF-83B0-7173CE1966F2}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1173,7 +957,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1204,7 +988,496 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>18</v>
+        <v>41</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>6</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22">
+        <v>46043</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="7"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="7"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A5:M5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22">
+        <v>46055</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5">
+        <v>1</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1265,8 +1538,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>16</v>
+      <c r="N5" s="25" t="s">
+        <v>14</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1297,7 +1570,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1328,7 +1601,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1364,8 +1637,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1417,7 +1690,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1448,7 +1721,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1510,7 +1783,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1541,7 +1814,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1572,7 +1845,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1608,8 +1881,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1661,7 +1934,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1754,7 +2027,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1785,7 +2058,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1852,8 +2125,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1904,8 +2177,8 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22">
-        <v>46082</v>
+      <c r="N2" s="22" t="s">
+        <v>26</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1935,8 +2208,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5">
-        <v>1</v>
+      <c r="N3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1967,7 +2240,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -1997,8 +2270,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5">
-        <v>2.1</v>
+      <c r="N5" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2029,7 +2302,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2060,7 +2333,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -2096,8 +2369,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2148,8 +2421,8 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22" t="s">
-        <v>29</v>
+      <c r="N2" s="22">
+        <v>46082</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -2179,8 +2452,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5" t="s">
-        <v>21</v>
+      <c r="N3" s="5">
+        <v>1</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -2241,8 +2514,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>30</v>
+      <c r="N5" s="5">
+        <v>2.1</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2273,7 +2546,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2304,7 +2577,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -2340,8 +2613,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA70D48-0F63-40A7-A614-2A774FBC305E}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2393,7 +2666,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -2424,7 +2697,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -2455,7 +2728,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -2486,7 +2759,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2517,7 +2790,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2548,7 +2821,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -2582,4 +2855,248 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA70D48-0F63-40A7-A614-2A774FBC305E}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>5</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
+++ b/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\DeSales\SWE\Documents\AndrewPrestaWeeklyLogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58657684-F074-4737-9654-1CF329F05F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12099779-6F5E-4997-B435-41A5274236EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="Mar 1 - Mar 8" sheetId="22" r:id="rId8"/>
     <sheet name="Mar 15 - Mar 22" sheetId="24" r:id="rId9"/>
     <sheet name="Mar 22 - Mar 29" sheetId="25" r:id="rId10"/>
-    <sheet name="Mar 29 - Apr 12" sheetId="26" r:id="rId11"/>
+    <sheet name="Mar 29 - Apr 5" sheetId="26" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -181,16 +181,18 @@
     <t>1, 4, 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1, </t>
-  </si>
-  <si>
     <t>Use Case #4: Using IDE</t>
   </si>
   <si>
-    <t>1. Met with the team to pick tasks and develop the Spring Planning document</t>
-  </si>
-  <si>
     <t>Sprint Planning, Use Case #4: Using IDE</t>
+  </si>
+  <si>
+    <t>1. Met with the team to pick tasks and develop the Spring Planning document.
+2. Worked with the team on minimal integration, further planning and accepting PRs.
+3. Successfully integrated IDE into the project. Further development is needed to complete the requirement including proper IDE integration and terminal support.</t>
+  </si>
+  <si>
+    <t>1, 3, 3</t>
   </si>
 </sst>
 </file>
@@ -775,7 +777,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -869,6 +871,739 @@
       <c r="M7" s="4"/>
       <c r="N7" s="5">
         <v>8</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD70740-6FBF-43AF-83B0-7173CE1966F2}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>7</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22">
+        <v>46043</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="7"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="7"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22">
+        <v>46055</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>1</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -904,8 +1639,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD70740-6FBF-43AF-83B0-7173CE1966F2}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -957,7 +1692,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -988,7 +1723,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1019,7 +1754,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -1049,8 +1784,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5">
-        <v>2.1</v>
+      <c r="N5" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1081,7 +1816,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1112,7 +1847,251 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
+        <v>2</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
         <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1148,12 +2127,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
@@ -1200,20 +2179,20 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22">
-        <v>46043</v>
-      </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="7"/>
+      <c r="N2" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -1231,253 +2210,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5">
-        <v>1</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="7"/>
-    </row>
-    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="18"/>
-    </row>
-    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5">
-        <v>1</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="N3:Y3"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="N7:Y7"/>
-    <mergeCell ref="N6:Y6"/>
-    <mergeCell ref="N5:Y5"/>
-    <mergeCell ref="A5:M5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
-    </row>
-    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="22">
-        <v>46055</v>
-      </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="24"/>
-    </row>
-    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5">
-        <v>1</v>
+      <c r="N3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1538,8 +2272,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="25" t="s">
-        <v>14</v>
+      <c r="N5" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1570,7 +2304,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1601,7 +2335,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1637,8 +2371,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1689,8 +2423,8 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22" t="s">
-        <v>17</v>
+      <c r="N2" s="22">
+        <v>46082</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1720,8 +2454,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5" t="s">
-        <v>18</v>
+      <c r="N3" s="5">
+        <v>1</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1752,7 +2486,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -1782,8 +2516,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>16</v>
+      <c r="N5" s="5">
+        <v>2.1</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1814,7 +2548,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1845,7 +2579,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1881,8 +2615,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1934,7 +2668,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1996,7 +2730,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -2027,7 +2761,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2058,7 +2792,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2125,8 +2859,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA70D48-0F63-40A7-A614-2A774FBC305E}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2178,7 +2912,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -2209,7 +2943,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -2240,7 +2974,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -2271,7 +3005,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2302,7 +3036,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2333,7 +3067,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -2367,736 +3101,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
-    </row>
-    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="22">
-        <v>46082</v>
-      </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="24"/>
-    </row>
-    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5">
-        <v>1</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="12"/>
-    </row>
-    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="18"/>
-    </row>
-    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5">
-        <v>1</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="N3:Y3"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N7:Y7"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="N5:Y5"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="N6:Y6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
-    </row>
-    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="24"/>
-    </row>
-    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="12"/>
-    </row>
-    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="18"/>
-    </row>
-    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5">
-        <v>3</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N7:Y7"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="N5:Y5"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="N6:Y6"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="N3:Y3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA70D48-0F63-40A7-A614-2A774FBC305E}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
-    </row>
-    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="24"/>
-    </row>
-    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="12"/>
-    </row>
-    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="18"/>
-    </row>
-    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5">
-        <v>5</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="N3:Y3"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N7:Y7"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="N5:Y5"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="N6:Y6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
+++ b/Documents/AndrewPrestaWeeklyLogs/PrestaAndrewWeeklogs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\DeSales\SWE\Documents\AndrewPrestaWeeklyLogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698F82C6-3B31-40CC-BAD9-0766971CA44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6049A108-3C89-4071-BF1C-A789DFEC3041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="861" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="14" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Mar 29 - Apr 5" sheetId="26" r:id="rId11"/>
     <sheet name="Apr 5 - Apr 12" sheetId="27" r:id="rId12"/>
     <sheet name="Apr 12 - Apr 19" sheetId="28" r:id="rId13"/>
+    <sheet name="Apr 19 - Apr 26" sheetId="29" r:id="rId14"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="56">
   <si>
     <t>Date on which you worked on the project.</t>
   </si>
@@ -220,6 +221,20 @@
     <t>1. Met with the team throughout the week to ensure the pieces come together correctly and each member is handling their parts.
 2. Worked on the IDE formatting to ensure it is clean and easy to use alongside the terminal.
 3. Planned the next week to create a next lesson button that clears the page and fills in with the next lesson.</t>
+  </si>
+  <si>
+    <t>4/20/2026, 4/22/2026, 4/24/2026</t>
+  </si>
+  <si>
+    <t>1. Held team meetings for feature discussions and worked on the IDE cleanup, where the editor and terminal are shown side-by-side in a smaller window. This was started in the last week but was finalized this week.
+2. Created a next lesson button that shows when a test has been submitted, which refreshes the window and displays the next lesson.
+3. Participated in a Sprint Review Meeting and explained my features of IDE cleanup and next lesson.</t>
+  </si>
+  <si>
+    <t>3, 4, 1</t>
+  </si>
+  <si>
+    <t>2.1, 2.2</t>
   </si>
 </sst>
 </file>
@@ -914,12 +929,6 @@
     <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="N3:Y3"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="N7:Y7"/>
     <mergeCell ref="A4:M4"/>
@@ -928,6 +937,12 @@
     <mergeCell ref="N5:Y5"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1142,6 +1157,494 @@
       <c r="M7" s="4"/>
       <c r="N7" s="5">
         <v>7</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48DED99C-B719-4EA4-9A73-9F11B6C66D9B}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>6</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC31E7F-7331-4AE5-9AF9-85CC78984272}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>5</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1177,8 +1680,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48DED99C-B719-4EA4-9A73-9F11B6C66D9B}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49BE2348-B0E0-431B-BE88-855D3B9BC18F}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1230,7 +1733,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -1261,251 +1764,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="12"/>
-    </row>
-    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="18"/>
-    </row>
-    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5">
-        <v>6</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="N3:Y3"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N7:Y7"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="N5:Y5"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="N6:Y6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC31E7F-7331-4AE5-9AF9-85CC78984272}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
-    </row>
-    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="24"/>
-    </row>
-    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1566,8 +1825,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5">
-        <v>2.1</v>
+      <c r="N5" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -1598,7 +1857,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -1629,7 +1888,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1890,6 +2149,12 @@
     <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A7:M7"/>
@@ -1898,12 +2163,6 @@
     <mergeCell ref="N6:Y6"/>
     <mergeCell ref="N5:Y5"/>
     <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="N3:Y3"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2119,6 +2378,250 @@
       <c r="M7" s="4"/>
       <c r="N7" s="5">
         <v>1</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
+        <v>2</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -2154,8 +2657,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0671443-C51E-42ED-B6E9-3EA401076830}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2207,7 +2710,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -2238,7 +2741,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -2300,7 +2803,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2331,7 +2834,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2362,7 +2865,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -2398,8 +2901,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA59DE7-9D52-4D8D-BB67-DCC7DF70561E}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2451,7 +2954,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -2544,7 +3047,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2575,7 +3078,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2642,8 +3145,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E44654-2DBA-4543-9F3B-8D1F4B41F219}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2694,8 +3197,8 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22" t="s">
-        <v>26</v>
+      <c r="N2" s="22">
+        <v>46082</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -2725,8 +3228,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5" t="s">
-        <v>21</v>
+      <c r="N3" s="5">
+        <v>1</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -2757,7 +3260,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -2787,8 +3290,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>24</v>
+      <c r="N5" s="5">
+        <v>2.1</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2819,7 +3322,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2850,7 +3353,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -2886,8 +3389,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9842BCB-B579-43DC-A36D-CBE39332E715}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2938,8 +3441,8 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="22">
-        <v>46082</v>
+      <c r="N2" s="22" t="s">
+        <v>29</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -2969,8 +3472,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="5">
-        <v>1</v>
+      <c r="N3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -3031,8 +3534,8 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="5">
-        <v>2.1</v>
+      <c r="N5" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -3063,7 +3566,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -3094,7 +3597,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -3130,8 +3633,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A607B5F4-3455-4DA9-A7A8-A29D8063057C}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA70D48-0F63-40A7-A614-2A774FBC305E}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3183,7 +3686,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="4"/>
       <c r="N2" s="22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
@@ -3214,7 +3717,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
       <c r="N3" s="5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -3245,7 +3748,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="4"/>
       <c r="N4" s="5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -3276,7 +3779,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
       <c r="N5" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -3307,7 +3810,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -3338,7 +3841,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="4"/>
       <c r="N7" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -3372,248 +3875,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA70D48-0F63-40A7-A614-2A774FBC305E}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:25" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
-    </row>
-    <row r="2" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="24"/>
-    </row>
-    <row r="3" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="12"/>
-    </row>
-    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="18"/>
-    </row>
-    <row r="7" spans="1:25" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5">
-        <v>5</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N7:Y7"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="N5:Y5"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="N6:Y6"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="N3:Y3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>